--- a/Fase 2/SIGMA_Burndown_Burnup.xlsx
+++ b/Fase 2/SIGMA_Burndown_Burnup.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -127,6 +127,17 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00404040"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -233,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -336,6 +347,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -504,7 +519,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -656,7 +671,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -843,7 +858,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -934,7 +949,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -967,7 +982,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -1088,7 +1103,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -1236,7 +1251,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -1424,7 +1439,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -1515,7 +1530,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -1548,7 +1563,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -1664,7 +1679,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -1816,7 +1831,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -2003,7 +2018,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -2094,7 +2109,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -2127,7 +2142,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -2248,7 +2263,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -2396,7 +2411,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -2584,7 +2599,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -2675,7 +2690,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -2708,7 +2723,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -2824,7 +2839,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -2952,7 +2967,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -3115,7 +3130,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -3206,7 +3221,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -3239,7 +3254,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -3359,7 +3374,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -3482,7 +3497,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -3645,7 +3660,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -3736,7 +3751,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -3769,7 +3784,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -3890,7 +3905,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -4038,7 +4053,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -4226,7 +4241,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -4317,7 +4332,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -4350,7 +4365,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -4466,7 +4481,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -4612,7 +4627,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -4793,7 +4808,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -4884,7 +4899,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -4917,7 +4932,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -5038,7 +5053,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -5180,7 +5195,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -5362,7 +5377,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -5453,7 +5468,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -5486,7 +5501,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -5602,7 +5617,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -5748,7 +5763,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -5929,7 +5944,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -6020,7 +6035,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -6053,7 +6068,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -6174,7 +6189,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -6316,7 +6331,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -6498,7 +6513,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -6589,7 +6604,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -6622,7 +6637,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -6738,7 +6753,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -6890,7 +6905,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -7077,7 +7092,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -7168,7 +7183,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -7201,7 +7216,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -7322,7 +7337,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -7470,7 +7485,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -7658,7 +7673,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -7749,7 +7764,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -7782,7 +7797,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -7898,7 +7913,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -8050,7 +8065,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CL"/>
               </a:p>
@@ -8237,7 +8252,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -8328,7 +8343,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -8361,7 +8376,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CL"/>
         </a:p>
@@ -9143,7 +9158,7 @@
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>1.0 · 28 de agosto de 2026</t>
+          <t>1.1 · 22-09-2026 · Sprints 1 a 3 con registro diario</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="34" min="1" max="1"/>
@@ -9762,7 +9777,9 @@
           <t>miércoles</t>
         </is>
       </c>
-      <c r="D8" s="28" t="n"/>
+      <c r="D8" s="28" t="n">
+        <v>5</v>
+      </c>
       <c r="E8" s="17">
         <f>$E7+$D8</f>
         <v/>
@@ -9796,7 +9813,9 @@
           <t>jueves</t>
         </is>
       </c>
-      <c r="D9" s="28" t="n"/>
+      <c r="D9" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="E9" s="13">
         <f>$E8+$D9</f>
         <v/>
@@ -9830,7 +9849,9 @@
           <t>viernes</t>
         </is>
       </c>
-      <c r="D10" s="28" t="n"/>
+      <c r="D10" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="E10" s="17">
         <f>$E9+$D10</f>
         <v/>
@@ -9864,7 +9885,9 @@
           <t>lunes</t>
         </is>
       </c>
-      <c r="D11" s="28" t="n"/>
+      <c r="D11" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="E11" s="13">
         <f>$E10+$D11</f>
         <v/>
@@ -9898,7 +9921,9 @@
           <t>martes</t>
         </is>
       </c>
-      <c r="D12" s="28" t="n"/>
+      <c r="D12" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="E12" s="17">
         <f>$E11+$D12</f>
         <v/>
@@ -9932,7 +9957,9 @@
           <t>miércoles</t>
         </is>
       </c>
-      <c r="D13" s="28" t="n"/>
+      <c r="D13" s="28" t="n">
+        <v>10</v>
+      </c>
       <c r="E13" s="13">
         <f>$E12+$D13</f>
         <v/>
@@ -9966,7 +9993,9 @@
           <t>jueves</t>
         </is>
       </c>
-      <c r="D14" s="28" t="n"/>
+      <c r="D14" s="28" t="n">
+        <v>15</v>
+      </c>
       <c r="E14" s="17">
         <f>$E13+$D14</f>
         <v/>
@@ -10000,7 +10029,9 @@
           <t>viernes</t>
         </is>
       </c>
-      <c r="D15" s="28" t="n"/>
+      <c r="D15" s="28" t="n">
+        <v>5</v>
+      </c>
       <c r="E15" s="13">
         <f>$E14+$D15</f>
         <v/>
@@ -10034,7 +10065,9 @@
           <t>lunes</t>
         </is>
       </c>
-      <c r="D16" s="28" t="n"/>
+      <c r="D16" s="28" t="n">
+        <v>14</v>
+      </c>
       <c r="E16" s="17">
         <f>$E15+$D16</f>
         <v/>
@@ -10068,7 +10101,9 @@
           <t>martes</t>
         </is>
       </c>
-      <c r="D17" s="28" t="n"/>
+      <c r="D17" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="13">
         <f>$E16+$D17</f>
         <v/>
@@ -10107,6 +10142,7 @@
       <c r="G18" s="19" t="n"/>
       <c r="H18" s="19" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="15" customHeight="1" s="34">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -10169,6 +10205,7 @@
         <v/>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="34">
       <c r="A27" s="35" t="inlineStr">
         <is>
@@ -10177,32 +10214,35 @@
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="34"/>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>Estado al 30-08-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="42" t="inlineStr">
-        <is>
-          <t>La curva sigue en cero y es correcto. El Sprint arranca el 02-09; el trabajo se construyó antes, durante el Sprint 0. Y aunque las 17 historias están construidas, ninguna cumple todavía la Definition of Done —faltan criterios verificados, validación de la PO y revisión de código—, así que no hay puntos que quemar. Se empieza a llenar cuando cada historia pase a Terminada en el Sprint Backlog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34"/>
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>Estado al 22-09-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="34">
+      <c r="A32" s="45" t="inlineStr">
+        <is>
+          <t>Sprint cerrado: las 17 historias comprometidas (81 puntos) están Terminada y sus 45 criterios de plataforma web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx, 49 casos). El único criterio de la aplicación móvil —HU-003 #3, el trabajo pendiente sin sincronizar— quedó reprogramado al Sprint 6 en la Sprint Review 1 y no resta puntos aquí. Lectura de la curva: el trabajo real fue por encima de la línea ideal —con retraso— hasta el día 6, cruzó por debajo el día 7 y llegó a cero el día 9; el día 10 se dedicó a la Sprint Review, donde la Product Owner aceptó las 16 historias que faltaban por aceptar. La columna amarilla se reconstruyó desde la Bitácora de Daily Scrum: cada historia quema sus puntos el último día en que el registro diario la nombra como trabajada, sin contar el día de la Sprint Review (ese día el equipo repasa todas para aceptarlas). Los puntos son los del Sprint Backlog y solo cuentan las historias Terminada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="34"/>
+    <row r="34" ht="15" customHeight="1" s="34"/>
+    <row r="35" ht="15" customHeight="1" s="34"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A32:H35"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A32:H34"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A27:H28"/>
@@ -10227,7 +10267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="34" min="1" max="1"/>
@@ -10369,7 +10409,9 @@
           <t>miércoles</t>
         </is>
       </c>
-      <c r="D8" s="28" t="n"/>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" s="17">
         <f>$E7+$D8</f>
         <v/>
@@ -10403,7 +10445,9 @@
           <t>jueves</t>
         </is>
       </c>
-      <c r="D9" s="28" t="n"/>
+      <c r="D9" s="28" t="n">
+        <v>13</v>
+      </c>
       <c r="E9" s="13">
         <f>$E8+$D9</f>
         <v/>
@@ -10437,7 +10481,9 @@
           <t>lunes</t>
         </is>
       </c>
-      <c r="D10" s="28" t="n"/>
+      <c r="D10" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="E10" s="17">
         <f>$E9+$D10</f>
         <v/>
@@ -10471,7 +10517,9 @@
           <t>martes</t>
         </is>
       </c>
-      <c r="D11" s="28" t="n"/>
+      <c r="D11" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="E11" s="13">
         <f>$E10+$D11</f>
         <v/>
@@ -10505,7 +10553,9 @@
           <t>miércoles</t>
         </is>
       </c>
-      <c r="D12" s="28" t="n"/>
+      <c r="D12" s="28" t="n">
+        <v>10</v>
+      </c>
       <c r="E12" s="17">
         <f>$E11+$D12</f>
         <v/>
@@ -10539,7 +10589,9 @@
           <t>jueves</t>
         </is>
       </c>
-      <c r="D13" s="28" t="n"/>
+      <c r="D13" s="28" t="n">
+        <v>13</v>
+      </c>
       <c r="E13" s="13">
         <f>$E12+$D13</f>
         <v/>
@@ -10573,7 +10625,9 @@
           <t>viernes</t>
         </is>
       </c>
-      <c r="D14" s="28" t="n"/>
+      <c r="D14" s="28" t="n">
+        <v>8</v>
+      </c>
       <c r="E14" s="17">
         <f>$E13+$D14</f>
         <v/>
@@ -10607,7 +10661,9 @@
           <t>lunes</t>
         </is>
       </c>
-      <c r="D15" s="28" t="n"/>
+      <c r="D15" s="28" t="n">
+        <v>13</v>
+      </c>
       <c r="E15" s="13">
         <f>$E14+$D15</f>
         <v/>
@@ -10641,7 +10697,9 @@
           <t>martes</t>
         </is>
       </c>
-      <c r="D16" s="28" t="n"/>
+      <c r="D16" s="28" t="n">
+        <v>10</v>
+      </c>
       <c r="E16" s="17">
         <f>$E15+$D16</f>
         <v/>
@@ -10680,6 +10738,7 @@
       <c r="G17" s="19" t="n"/>
       <c r="H17" s="19" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="34">
       <c r="A19" s="4" t="inlineStr">
         <is>
@@ -10742,6 +10801,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="15" customHeight="1" s="34">
       <c r="A26" s="35" t="inlineStr">
         <is>
@@ -10750,8 +10810,25 @@
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="34"/>
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>Estado al 22-09-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="34">
+      <c r="A29" s="45" t="inlineStr">
+        <is>
+          <t>Sprint cerrado en su alcance web: 18 historias y 83 puntos Terminada, 42 criterios verificados (SIGMA_Informe_Pruebas_Sprint_2.docx, 53 casos). Las cuatro historias de aplicación móvil —HU-150, HU-043, HU-154 y HU-044, 26 puntos— se movieron al Sprint 6 en la Sprint Review 1 y por eso el compromiso de este Sprint quedó en 83 y no en los 109 planificados. Lectura de la curva: el trabajo real fue por encima de la ideal todo el Sprint —el máximo retraso fue de 8 puntos el día 4— y recién cerró en cero el último día. La columna amarilla se reconstruyó desde la Bitácora de Daily Scrum: cada historia quema sus puntos el último día en que el registro diario la nombra como trabajada, sin contar el día de la Sprint Review (ese día el equipo repasa todas para aceptarlas). Los puntos son los del Sprint Backlog y solo cuentan las historias Terminada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="34"/>
+    <row r="31" ht="15" customHeight="1" s="34"/>
+    <row r="32" ht="15" customHeight="1" s="34"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A20:B20"/>
@@ -10759,6 +10836,7 @@
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A26:H27"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A29:H32"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -10783,7 +10861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="34" min="1" max="1"/>
@@ -10925,7 +11003,9 @@
           <t>miércoles</t>
         </is>
       </c>
-      <c r="D8" s="28" t="n"/>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="E8" s="17">
         <f>$E7+$D8</f>
         <v/>
@@ -10959,7 +11039,9 @@
           <t>jueves</t>
         </is>
       </c>
-      <c r="D9" s="28" t="n"/>
+      <c r="D9" s="28" t="n">
+        <v>13</v>
+      </c>
       <c r="E9" s="13">
         <f>$E8+$D9</f>
         <v/>
@@ -10993,7 +11075,9 @@
           <t>viernes</t>
         </is>
       </c>
-      <c r="D10" s="28" t="n"/>
+      <c r="D10" s="28" t="n">
+        <v>13</v>
+      </c>
       <c r="E10" s="17">
         <f>$E9+$D10</f>
         <v/>
@@ -11027,7 +11111,9 @@
           <t>lunes</t>
         </is>
       </c>
-      <c r="D11" s="28" t="n"/>
+      <c r="D11" s="28" t="n">
+        <v>11</v>
+      </c>
       <c r="E11" s="13">
         <f>$E10+$D11</f>
         <v/>
@@ -11061,7 +11147,9 @@
           <t>martes</t>
         </is>
       </c>
-      <c r="D12" s="28" t="n"/>
+      <c r="D12" s="28" t="n">
+        <v>18</v>
+      </c>
       <c r="E12" s="17">
         <f>$E11+$D12</f>
         <v/>
@@ -11095,7 +11183,9 @@
           <t>miércoles</t>
         </is>
       </c>
-      <c r="D13" s="28" t="n"/>
+      <c r="D13" s="28" t="n">
+        <v>13</v>
+      </c>
       <c r="E13" s="13">
         <f>$E12+$D13</f>
         <v/>
@@ -11129,7 +11219,9 @@
           <t>jueves</t>
         </is>
       </c>
-      <c r="D14" s="28" t="n"/>
+      <c r="D14" s="28" t="n">
+        <v>21</v>
+      </c>
       <c r="E14" s="17">
         <f>$E13+$D14</f>
         <v/>
@@ -11163,7 +11255,9 @@
           <t>viernes</t>
         </is>
       </c>
-      <c r="D15" s="28" t="n"/>
+      <c r="D15" s="28" t="n">
+        <v>34</v>
+      </c>
       <c r="E15" s="13">
         <f>$E14+$D15</f>
         <v/>
@@ -11197,7 +11291,9 @@
           <t>martes</t>
         </is>
       </c>
-      <c r="D16" s="28" t="n"/>
+      <c r="D16" s="28" t="n">
+        <v>16</v>
+      </c>
       <c r="E16" s="17">
         <f>$E15+$D16</f>
         <v/>
@@ -11236,6 +11332,7 @@
       <c r="G17" s="19" t="n"/>
       <c r="H17" s="19" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="34">
       <c r="A19" s="4" t="inlineStr">
         <is>
@@ -11298,6 +11395,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="15" customHeight="1" s="34">
       <c r="A26" s="35" t="inlineStr">
         <is>
@@ -11306,8 +11404,25 @@
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="34"/>
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>Estado al 22-09-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="34">
+      <c r="A29" s="45" t="inlineStr">
+        <is>
+          <t>Sprint cerrado en su alcance web: 28 historias y 139 puntos Terminada, 73 criterios verificados (SIGMA_Informe_Pruebas_Sprint_3.docx, 87 casos). HU-151 «Trabajar sin conexión» (13 puntos) se movió al Sprint 6. Las seis historias que entraron tarde al Sprint —HU-059, 066, 067, 068, 069 y 077— recibieron sus criterios de aceptación el 22-09-2026 y se probaron completas. Lectura de la curva: es el Sprint más cargado (139 puntos frente a los 81 y 83 anteriores) y se nota; el retraso llegó a 25 puntos el día 4 y se recuperó en los dos últimos días, con 50 puntos cerrados entre el día 8 y el 9. Cerró completo, pero sin holgura. La columna amarilla se reconstruyó desde la Bitácora de Daily Scrum: cada historia quema sus puntos el último día en que el registro diario la nombra como trabajada, sin contar el día de la Sprint Review (ese día el equipo repasa todas para aceptarlas). Los puntos son los del Sprint Backlog y solo cuentan las historias Terminada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="34"/>
+    <row r="31" ht="15" customHeight="1" s="34"/>
+    <row r="32" ht="15" customHeight="1" s="34"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A20:B20"/>
@@ -11315,6 +11430,7 @@
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A26:H27"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A29:H32"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
